--- a/UTCUTS/A1_Inputs/A-I_Classifier_Modes_Transport.xlsx
+++ b/UTCUTS/A1_Inputs/A-I_Classifier_Modes_Transport.xlsx
@@ -1051,7 +1051,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E50605C8-83E2-4B32-86E6-D61AACF712F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB4D5488-C37B-4F9B-A1CC-8CF73ACBAD09}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
